--- a/SOA-C03/SOA-C03-ExamTopics-Questions.xlsx
+++ b/SOA-C03/SOA-C03-ExamTopics-Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/Learn-AI-MCP_ML/SOA-C03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="542" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE4361D-3581-4290-965D-AFE092E3CEC4}"/>
+  <xr:revisionPtr revIDLastSave="543" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBADE943-6160-42DA-A907-998034BE66F4}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
@@ -587,7 +587,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -626,6 +626,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -656,10 +664,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -682,12 +691,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -2726,7 +2735,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>179</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -3409,7 +3418,7 @@
       <c r="A77" s="1">
         <v>75</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" t="s">
         <v>120</v>
       </c>
     </row>
@@ -4358,6 +4367,9 @@
   <conditionalFormatting sqref="B2:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{E4BE23F5-8686-4318-92B6-7D7B715CDD5E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SOA-C03/SOA-C03-ExamTopics-Questions.xlsx
+++ b/SOA-C03/SOA-C03-ExamTopics-Questions.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/Learn-AI-MCP_ML/SOA-C03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="543" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBADE943-6160-42DA-A907-998034BE66F4}"/>
+  <xr:revisionPtr revIDLastSave="584" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1D2C752-F2BF-4E30-8616-AFA9E65B6DDD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
+    <workbookView xWindow="-28920" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
   <sheets>
     <sheet name="ExamTopics" sheetId="4" r:id="rId1"/>
     <sheet name="ExamTopics (SOA-C03)" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ExamTopics!$A$5:$C$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ExamTopics!$A$5:$E$241</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ExamTopics (SOA-C03)'!$A$2:$S$202</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="180">
   <si>
     <t>No</t>
   </si>
@@ -699,7 +699,47 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1060,15 +1100,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}">
-  <dimension ref="A1:D241"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
@@ -1077,7 +1118,7 @@
       </c>
       <c r="D1" s="7"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="str">
         <f>TEXT(COUNTIF(B5:B242,"Yes")/COUNTA(B5:B242),"0.00%")</f>
         <v>70.97%</v>
@@ -1090,8 +1131,12 @@
         <f>TEXT(COUNTIF(D5:D242,"Yes")/COUNTA(D5:D242),"0.00%")</f>
         <v>61.29%</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="str">
+        <f>TEXT(COUNTIF(E5:E242,"Yes")/COUNTA(E5:E242),"0.00%")</f>
+        <v>88.78%</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1107,8 +1152,12 @@
         <f>COUNTIF(D6:D243,"Yes")</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="4">
+        <f>COUNTIF(E6:E243,"Yes")</f>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,8 +1173,12 @@
         <f>COUNTIF(D7:D244,"No")</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="3">
+        <f>COUNTIF(E7:E244,"No")</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1136,10 +1189,13 @@
         <v>25082026</v>
       </c>
       <c r="D5">
-        <v>26082027</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>26082026</v>
+      </c>
+      <c r="E5">
+        <v>2092026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1149,8 +1205,11 @@
       <c r="C6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1160,8 +1219,11 @@
       <c r="C7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1171,8 +1233,11 @@
       <c r="C8" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1182,8 +1247,11 @@
       <c r="C9" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1193,8 +1261,11 @@
       <c r="C10" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1204,8 +1275,11 @@
       <c r="C11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -1215,8 +1289,11 @@
       <c r="C12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>8</v>
       </c>
@@ -1226,8 +1303,11 @@
       <c r="C13" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -1237,8 +1317,11 @@
       <c r="C14" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -1248,8 +1331,11 @@
       <c r="C15" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>11</v>
       </c>
@@ -1259,8 +1345,11 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>12</v>
       </c>
@@ -1270,8 +1359,11 @@
       <c r="C17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>13</v>
       </c>
@@ -1281,8 +1373,11 @@
       <c r="C18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>14</v>
       </c>
@@ -1292,8 +1387,11 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -1303,8 +1401,11 @@
       <c r="C20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>16</v>
       </c>
@@ -1314,8 +1415,11 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>17</v>
       </c>
@@ -1325,8 +1429,11 @@
       <c r="C22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>18</v>
       </c>
@@ -1336,8 +1443,11 @@
       <c r="C23" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>19</v>
       </c>
@@ -1347,8 +1457,11 @@
       <c r="C24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>20</v>
       </c>
@@ -1358,8 +1471,11 @@
       <c r="C25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>21</v>
       </c>
@@ -1369,8 +1485,11 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>22</v>
       </c>
@@ -1380,8 +1499,11 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>23</v>
       </c>
@@ -1391,8 +1513,11 @@
       <c r="C28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>24</v>
       </c>
@@ -1402,8 +1527,11 @@
       <c r="C29" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>25</v>
       </c>
@@ -1413,8 +1541,11 @@
       <c r="C30" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>26</v>
       </c>
@@ -1424,8 +1555,11 @@
       <c r="C31" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -1435,8 +1569,11 @@
       <c r="C32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>28</v>
       </c>
@@ -1446,8 +1583,11 @@
       <c r="C33" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>29</v>
       </c>
@@ -1457,8 +1597,11 @@
       <c r="C34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>30</v>
       </c>
@@ -1468,1255 +1611,1767 @@
       <c r="C35" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>31</v>
       </c>
       <c r="C36" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>32</v>
       </c>
       <c r="C37" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>33</v>
       </c>
       <c r="C38" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>34</v>
       </c>
       <c r="C39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>35</v>
       </c>
       <c r="C40" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>36</v>
       </c>
       <c r="C41" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>37</v>
       </c>
       <c r="C42" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>38</v>
       </c>
       <c r="C43" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>39</v>
       </c>
       <c r="C44" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>40</v>
       </c>
       <c r="C45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>41</v>
       </c>
       <c r="C46" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E46" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>42</v>
       </c>
       <c r="C47" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>43</v>
       </c>
       <c r="C48" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>44</v>
       </c>
       <c r="C49" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E49" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45</v>
       </c>
       <c r="C50" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46</v>
       </c>
       <c r="C51" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>47</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>48</v>
       </c>
       <c r="C53" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E53" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>49</v>
       </c>
       <c r="C54" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>50</v>
       </c>
       <c r="C55" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E55" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>51</v>
       </c>
       <c r="C56" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E56" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>52</v>
       </c>
       <c r="C57" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>53</v>
       </c>
       <c r="C58" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>54</v>
       </c>
       <c r="C59" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E59" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>55</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>56</v>
       </c>
       <c r="C61" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>57</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>58</v>
       </c>
       <c r="C63" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E63" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>59</v>
       </c>
       <c r="C64" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>60</v>
       </c>
       <c r="C65" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>61</v>
       </c>
       <c r="C66" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>62</v>
       </c>
       <c r="C67" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>63</v>
       </c>
       <c r="C68" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>64</v>
       </c>
       <c r="C69" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E69" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>65</v>
       </c>
       <c r="C70" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E70" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>66</v>
       </c>
       <c r="C71" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>67</v>
       </c>
       <c r="C72" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>68</v>
       </c>
       <c r="C73" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>69</v>
       </c>
       <c r="C74" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E74" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>70</v>
       </c>
       <c r="C75" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>71</v>
       </c>
       <c r="D76" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>72</v>
       </c>
       <c r="D77" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E77" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>73</v>
       </c>
       <c r="D78" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E78" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>74</v>
       </c>
       <c r="D79" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E79" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>75</v>
       </c>
       <c r="D80" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E80" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>76</v>
       </c>
       <c r="D81" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E81" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>77</v>
       </c>
       <c r="D82" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E82" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>78</v>
       </c>
       <c r="D83" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E83" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>79</v>
       </c>
       <c r="D84" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E84" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>80</v>
       </c>
       <c r="D85" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E85" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>81</v>
       </c>
       <c r="D86" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E86" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>82</v>
       </c>
       <c r="D87" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E87" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>83</v>
       </c>
       <c r="D88" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>84</v>
       </c>
       <c r="D89" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E89" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>85</v>
       </c>
       <c r="D90" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>86</v>
       </c>
       <c r="D91" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E91" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>87</v>
       </c>
       <c r="D92" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E92" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>88</v>
       </c>
       <c r="D93" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E93" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>89</v>
       </c>
       <c r="D94" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E94" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>90</v>
       </c>
       <c r="D95" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E95" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>91</v>
       </c>
       <c r="D96" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E96" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>92</v>
       </c>
       <c r="D97" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E97" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>93</v>
       </c>
       <c r="D98" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E98" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>94</v>
       </c>
       <c r="D99" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E99" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>95</v>
       </c>
       <c r="D100" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E100" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>96</v>
       </c>
       <c r="D101" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E101" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>97</v>
       </c>
       <c r="D102" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E102" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>98</v>
       </c>
       <c r="D103" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E103" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>99</v>
       </c>
       <c r="D104" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E104" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>100</v>
       </c>
       <c r="D105" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E105" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E106" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>102</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E107" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>103</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E108" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>104</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E109" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>105</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E110" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>106</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E111" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>107</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E112" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>108</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E113" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>109</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E114" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>110</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E115" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>111</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E116" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>112</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E117" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>113</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E118" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>114</v>
       </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E119" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>115</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E120" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>116</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E121" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>117</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E122" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>118</v>
       </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E123" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>119</v>
       </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E124" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E125" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>121</v>
       </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E126" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>122</v>
       </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E127" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>123</v>
       </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E128" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>124</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E129" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>125</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E130" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>126</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E131" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>127</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E132" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>128</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E133" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>129</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E134" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>130</v>
       </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E135" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>131</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E136" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>132</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E137" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>133</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E138" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>134</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E139" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>135</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E140" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>136</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E141" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>137</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E142" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>138</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E143" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>139</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E144" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>140</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E145" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>141</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E146" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>142</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E147" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>143</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E148" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>144</v>
       </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E149" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>145</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E150" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>146</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E151" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>147</v>
       </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E152" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>148</v>
       </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E153" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>149</v>
       </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E154" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E155" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>151</v>
       </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E156" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>152</v>
       </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E157" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>153</v>
       </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E158" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>154</v>
       </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E159" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>155</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E160" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>156</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E161" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>157</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E162" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>158</v>
       </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E163" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>159</v>
       </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E164" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>160</v>
       </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E165" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>161</v>
       </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E166" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>162</v>
       </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E167" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>163</v>
       </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E168" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>164</v>
       </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E169" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>165</v>
       </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E170" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>166</v>
       </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E171" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>167</v>
       </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E172" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>168</v>
       </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E173" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>169</v>
       </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E174" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>170</v>
       </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E175" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>171</v>
       </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E176" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>172</v>
       </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E177" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>173</v>
       </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E178" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>174</v>
       </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E179" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>175</v>
       </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E180" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>176</v>
       </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E181" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>177</v>
       </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E182" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>178</v>
       </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E183" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>179</v>
       </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E184" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>180</v>
       </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E185" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>181</v>
       </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E186" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>182</v>
       </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E187" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>183</v>
       </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E188" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>184</v>
       </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E189" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>185</v>
       </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E190" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>186</v>
       </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E191" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>187</v>
       </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E192" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>188</v>
       </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E193" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>189</v>
       </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E194" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>190</v>
       </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E195" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>191</v>
       </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E196" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>192</v>
       </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E197" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>193</v>
       </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E198" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>194</v>
       </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E199" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>195</v>
       </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E200" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>196</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>197</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>198</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>214</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>215</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>217</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>218</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>219</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>233</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>234</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>235</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>236</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:C241" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}"/>
+  <autoFilter ref="A5:E241" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="No"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C6:C75 B6:B1048576 D76:D105">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",B6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",B6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E200">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",E6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",E6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4365,7 +5020,7 @@
   </sheetData>
   <autoFilter ref="A2:S202" xr:uid="{44E3CCDD-CECD-4B29-8FAC-EFB87C60FE25}"/>
   <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{E4BE23F5-8686-4318-92B6-7D7B715CDD5E}"/>
